--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:10</t>
+    <t xml:space="preserve">2026-09-09 23:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:04</t>
+    <t xml:space="preserve">2026-09-17 14:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:01</t>
+    <t xml:space="preserve">2026-09-23 12:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:30</t>
+    <t xml:space="preserve">2026-10-02 14:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:15</t>
+    <t xml:space="preserve">2026-10-04 08:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_aysen.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_aysen.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:53</t>
+    <t xml:space="preserve">2026-10-05 10:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -525,7 +525,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1058221.62</v>
+        <v>1058221.63</v>
       </c>
     </row>
     <row r="4">
@@ -610,7 +610,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>936954.62</v>
+        <v>936954.63</v>
       </c>
     </row>
     <row r="9">
@@ -661,7 +661,7 @@
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>780323.62</v>
+        <v>780323.63</v>
       </c>
     </row>
   </sheetData>
